--- a/01-tavares-claims-grc-program/artifacts/nist_csf_gap_assessment.xlsx
+++ b/01-tavares-claims-grc-program/artifacts/nist_csf_gap_assessment.xlsx
@@ -633,11 +633,10 @@
     <row r="2" ht="15" customHeight="1" s="26">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Assessed against NIST Cybersecurity Framework 2.0 | Assessment date: 2026-02-01 | Fictional organization. Created for portfolio demonstration purposes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Assessed against NIST Cybersecurity Framework 2.0 | Assessment date: 2026-02-06 | Fictional organization. Created for portfolio demonstration purposes.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="23.85" customHeight="1" s="26">
       <c r="A4" s="29" t="inlineStr">
         <is>
@@ -1772,7 +1771,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="26">
       <c r="A3" s="38" t="inlineStr">
         <is>
